--- a/human_validation/judge/kor/judge_D002_S001_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D002_S001_P003__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,230 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 방문하셨는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 네, 가장 큰 문제는 지속적으로 정신적 노력이 필요한 일들을 할 때 정말 힘들다는 거예요. 예를 들어 회사에서 월간 보고서를 작성하거나 여러 지역에 걸친 보건 행사처럼 좀 더 큰 걸 계획해야 할 때, 마치 벽에 부딪힌 것 같은 느낌이 들어요. 중요하다는 건 알면서도 계속 미루게 되고, 그게 점점 진짜 문제가 되고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 특별한 이유가 없는데도 지나치게 걱정이 되거나 불안한 느낌이 드는 경우가 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 그건 아닌 것 같아요. 뭔가 실제로 진행 중인 일, 그러니까 마감이나 회사 문제 같은 게 있을 때는 걱정하긴 하는데, 뚜렷한 이유 없이 불안하다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 특별한 업무 스트레스가 없을 때도 기분이 가라앉거나 우울하다고 느끼거나, 평소에 즐기던 활동에 흥미를 잃은 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 그런 건 아닌 것 같아요. 전반적으로 우울하다거나 뭔가에 흥미를 잃었다는 느낌은 딱히 없었어요. 그보다는 일이 쌓였을 때 답답함을 느끼는 정도지, 그 외에는 이유 없이 기분이 가라앉는다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 업무 외에 개인적인 일 처리나 집안일, 친구들과의 약속을 지키는 것처럼 삶의 다른 영역에서도 비슷하게 정리정돈이나 일 처리에 어려움을 겪으시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네, 꼭 업무 관련 일이 아니어도 그래요. 회사 프로젝트랑 추모 위원회 일, 봉사 행사 같은 걸 동시에 처리하다 보면 메모가 세 군데에 흩어져 있고, 그러면 뭘 먼저 해야 할지 정리가 안 돼요. 결국 일을 너무 늦게까지 미루다가 막판에 몰아서 하게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 학창 시절부터 지금까지 살아오시면서 계속 정리정돈이나 할 일을 챙기는 데 어려움이 있었거나, 물건을 자주 잃어버리는 편이었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네, 꽤 오래전부터 그랬어요. 초등학교 때도 선생님들이 부모님께 제가 똑똑한데 늘 딴생각을 하거나 학습지를 잃어버린다고 말씀하셨대요. 엄마가 매일 밤 가방을 확인해 주지 않으면 숙제를 못 낼 때도 있었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (복합형) (D001) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 직장 외에 집이나 운전 중, 친구들과 대화할 때처럼 업무와 관련 없는 상황에서도 집중하거나 정리정돈을 유지하는 데 어려움을 겪으시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네, 그래요. 회의 중에도 예산 업데이트 같은 걸 따라가려고 하다가 전화 진동이 울리거나 복도에서 사람들이 이야기하는 소리, 아니면 리그 관련해서 깜빡한 게 갑자기 생각나면 거기에 정신이 팔려요. 그러다 보면 몇 분 동안 무슨 얘기가 오갔는지 놓쳤다는 걸 깨닫게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (복합형) (D001) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 가만히 있거나 조용히 있어야 하는 상황에서 특히 안절부절못하거나 몸을 가만두지 못하거나 자리에 앉아 있기 힘든 경우가 자주 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 그건 아닌 것 같아요. 그러니까, 다른 사람들처럼 가끔 의자에서 자세를 바꾸긴 하는데, 유난히 안절부절못하거나 앉아 있어야 할 때 앉아 있지 못한다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 이런 집중력과 정리정돈 문제가 사회생활이나 업무, 혹은 삶의 다른 중요한 부분에서 문제를 일으키고 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네, 그래요. 그러니까 아직은 그럭저럭 지내고 있어요. 회사도 다니고 지역사회 활동도 하고 있으니까요. 그런데 문제가 생기긴 해요. 제가 놓치거나 잊어버린 일을 다른 사람들이 대신 처리해 줘야 했고, 제가 제때 신경 쓰지 못해서 마감을 놓친 적도 있어요.
+사회적으로도 제가 실수한 것 때문에 동료나 친구들에게 막판에 사과해야 했던 적이 있어서, 그게 좀 창피해요. 모든 게 다 무너지고 있다는 건 아니지만, 확실히 저한테 영향을 미치고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 이런 집중력이나 일 처리 문제가 집, 사회적 상황, 직장처럼 여러 곳에서 나타나나요, 아니면 특정한 한 곳에서만 나타나나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 여러 곳에서 나타나요. 직장에서도 느끼지만, 직장 밖 사람들과의 관계에서도 그래요. 아직 그럭저럭 지내고는 있는데, 빈틈이 있어요. 제가 뭔가를 놓쳤을 때 다른 사람들이 대신 처리해 줘야 했고, 마감을 놓친 적도 있고, 동료나 친구들에게 막판에 사과해야 했던 적도 있어요. 솔직히 좀 창피해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 중요한 일에 집중하려고 할 때도 주변의 소리나 눈에 보이는 것들, 혹은 본인의 생각 때문에 자주 산만해지시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네, 꽤 자주 그래요. 회의 중에 예산 업데이트를 들으려고 하다가 전화가 진동하거나 복도에서 사람들 얘기하는 소리가 들리면 잠깐 정신이 딴 데로 가버려요. 어떨 때는 외부 자극이 아니라, 리그 관련해서 깜빡한 일이 갑자기 떠올라서 그러기도 하고요. 그러고 나면 몇 분 동안 무슨 얘기가 오갔는지 놓쳤다는 걸 깨달아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>진단명: 주의력결핍 과잉행동장애 (부주의 우세형) (D002)
 인구통계: 성별 남성 / 나이 46 / 직업상태 medical or health services manager / 최종학력 전문학사
@@ -575,288 +790,44 @@
 증상 지속 기간: 1 year and 11 months
 추가 요건: Onset prior to age 12 years
 주호소 증상 코드: S006
-배경 서술: 후안은 자신과 함께 지역 보건 행사에서 자원봉사를 하기도 했던 축구 리그 친구가 세상을 떠난 후 증상이 나타나기 시작했다. 그는 친구를 추모하는 행사와 리그 운영, 지역 봉사 활동에서 여러 조직 업무를 떠맡게 되었다. 이후 1년 11개월 동안, 늘어난 책임들이 그동안 그를 지탱해 주던 체크리스트 기반의 시스템을 흔들어 놓았다. 그는 점점 사소한 계획 실수를 저지르고, 여러 장소가 얽힌 프로젝트를 정리하는 데 어려움을 겪었으며, 정신적으로 부담이 큰 보고서 작성을 미루고, 회의 중 집중력을 잃고, 전화나 지역사회 약속을 잊어버리고, 사회적 상황을 만회하려 할 때 말이 지나치게 많아지는 모습을 보였다. 장애의 정도는 중등도였다. 그는 여전히 직장을 유지하고 있었고 주변의 신뢰도 받고 있었지만, 마감을 놓치는 일이 생겼고 동료들은 늘 꼼꼼했던 그의 업무 처리에서 일관성이 흔들리는 것을 알아차렸으며, 친구들은 약속을 지키지 못한 데 대한 막판 사과를 받는 일이 잦아졌다. 결국 후안은 스프레드시트와 알림만으로는 더 이상 업무와 지역사회 책임을 감당할 수 없다는 것을 깨닫고, 주치의에게 정신과 진료 의뢰를 요청했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 방문하셨는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 네, 가장 큰 문제는 지속적으로 정신적 노력이 필요한 일들을 할 때 정말 힘들다는 거예요. 예를 들어 회사에서 월간 보고서를 작성하거나 여러 지역에 걸친 보건 행사처럼 좀 더 큰 걸 계획해야 할 때, 마치 벽에 부딪힌 것 같은 느낌이 들어요. 중요하다는 건 알면서도 계속 미루게 되고, 그게 점점 진짜 문제가 되고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 특별한 이유가 없는데도 지나치게 걱정이 되거나 불안한 느낌이 드는 경우가 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 그건 아닌 것 같아요. 뭔가 실제로 진행 중인 일, 그러니까 마감이나 회사 문제 같은 게 있을 때는 걱정하긴 하는데, 뚜렷한 이유 없이 불안하다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 특별한 업무 스트레스가 없을 때도 기분이 가라앉거나 우울하다고 느끼거나, 평소에 즐기던 활동에 흥미를 잃은 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 그런 건 아닌 것 같아요. 전반적으로 우울하다거나 뭔가에 흥미를 잃었다는 느낌은 딱히 없었어요. 그보다는 일이 쌓였을 때 답답함을 느끼는 정도지, 그 외에는 이유 없이 기분이 가라앉는다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 업무 외에 개인적인 일 처리나 집안일, 친구들과의 약속을 지키는 것처럼 삶의 다른 영역에서도 비슷하게 정리정돈이나 일 처리에 어려움을 겪으시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네, 꼭 업무 관련 일이 아니어도 그래요. 회사 프로젝트랑 추모 위원회 일, 봉사 행사 같은 걸 동시에 처리하다 보면 메모가 세 군데에 흩어져 있고, 그러면 뭘 먼저 해야 할지 정리가 안 돼요. 결국 일을 너무 늦게까지 미루다가 막판에 몰아서 하게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 학창 시절부터 지금까지 살아오시면서 계속 정리정돈이나 할 일을 챙기는 데 어려움이 있었거나, 물건을 자주 잃어버리는 편이었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네, 꽤 오래전부터 그랬어요. 초등학교 때도 선생님들이 부모님께 제가 똑똑한데 늘 딴생각을 하거나 학습지를 잃어버린다고 말씀하셨대요. 엄마가 매일 밤 가방을 확인해 주지 않으면 숙제를 못 낼 때도 있었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 직장 외에 집이나 운전 중, 친구들과 대화할 때처럼 업무와 관련 없는 상황에서도 집중하거나 정리정돈을 유지하는 데 어려움을 겪으시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네, 그래요. 회의 중에도 예산 업데이트 같은 걸 따라가려고 하다가 전화 진동이 울리거나 복도에서 사람들이 이야기하는 소리, 아니면 리그 관련해서 깜빡한 게 갑자기 생각나면 거기에 정신이 팔려요. 그러다 보면 몇 분 동안 무슨 얘기가 오갔는지 놓쳤다는 걸 깨닫게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 가만히 있거나 조용히 있어야 하는 상황에서 특히 안절부절못하거나 몸을 가만두지 못하거나 자리에 앉아 있기 힘든 경우가 자주 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 그건 아닌 것 같아요. 그러니까, 다른 사람들처럼 가끔 의자에서 자세를 바꾸긴 하는데, 유난히 안절부절못하거나 앉아 있어야 할 때 앉아 있지 못한다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 이런 집중력과 정리정돈 문제가 사회생활이나 업무, 혹은 삶의 다른 중요한 부분에서 문제를 일으키고 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네, 그래요. 그러니까 아직은 그럭저럭 지내고 있어요. 회사도 다니고 지역사회 활동도 하고 있으니까요. 그런데 문제가 생기긴 해요. 제가 놓치거나 잊어버린 일을 다른 사람들이 대신 처리해 줘야 했고, 제가 제때 신경 쓰지 못해서 마감을 놓친 적도 있어요.
-사회적으로도 제가 실수한 것 때문에 동료나 친구들에게 막판에 사과해야 했던 적이 있어서, 그게 좀 창피해요. 모든 게 다 무너지고 있다는 건 아니지만, 확실히 저한테 영향을 미치고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 이런 집중력이나 일 처리 문제가 집, 사회적 상황, 직장처럼 여러 곳에서 나타나나요, 아니면 특정한 한 곳에서만 나타나나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 여러 곳에서 나타나요. 직장에서도 느끼지만, 직장 밖 사람들과의 관계에서도 그래요. 아직 그럭저럭 지내고는 있는데, 빈틈이 있어요. 제가 뭔가를 놓쳤을 때 다른 사람들이 대신 처리해 줘야 했고, 마감을 놓친 적도 있고, 동료나 친구들에게 막판에 사과해야 했던 적도 있어요. 솔직히 좀 창피해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 중요한 일에 집중하려고 할 때도 주변의 소리나 눈에 보이는 것들, 혹은 본인의 생각 때문에 자주 산만해지시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네, 꽤 자주 그래요. 회의 중에 예산 업데이트를 들으려고 하다가 전화가 진동하거나 복도에서 사람들 얘기하는 소리가 들리면 잠깐 정신이 딴 데로 가버려요. 어떨 때는 외부 자극이 아니라, 리그 관련해서 깜빡한 일이 갑자기 떠올라서 그러기도 하고요. 그러고 나면 몇 분 동안 무슨 얘기가 오갔는지 놓쳤다는 걸 깨달아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
+배경 서술: 후안은 자신과 함께 지역 보건 행사에서 자원봉사를 하기도 했던 축구 리그 친구가 세상을 떠난 후 증상이 나타나기 시작했다. 그는 친구를 추모하는 행사와 리그 운영, 지역 봉사 활동에서 여러 조직 업무를 떠맡게 되었다. 이후 1년 11개월 동안, 늘어난 책임들이 그동안 그를 지탱해 주던 체크리스트 기반의 시스템을 흔들어 놓았다. 그는 점점 사소한 계획 실수를 저지르고, 여러 장소가 얽힌 프로젝트를 정리하는 데 어려움을 겪었으며, 정신적으로 부담이 큰 보고서 작성을 미루고, 회의 중 집중력을 잃고, 전화나 지역사회 약속을 잊어버리고, 사회적 상황을 만회하려 할 때 말이 지나치게 많아지는 모습을 보였다. 장애의 정도는 중등도였다. 그는 여전히 직장을 유지하고 있었고 주변의 신뢰도 받고 있었지만, 마감을 놓치는 일이 생겼고 동료들은 늘 꼼꼼했던 그의 업무 처리에서 일관성이 흔들리는 것을 알아차렸으며, 친구들은 약속을 지키지 못한 데 대한 막판 사과를 받는 일이 잦아졌다. 결국 후안은 스프레드시트와 알림만으로는 더 이상 업무와 지역사회 책임을 감당할 수 없다는 것을 깨닫고, 주치의에게 정신과 진료 의뢰를 요청했다.
+표집된 증상 목록:
+  - S001 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.
+  - S005 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.
+  - S006 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.
+  - S008 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).
+  - S009 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).
+  - S015 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.</t>
+        </is>
+      </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: inattention (관계=must_include, 요구개수=5, 충족개수=8, 커버리지=1.0)
-  확인된 근거: 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.; 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.; 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.; 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.; 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.; 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.; 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).; 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).
-  누락: 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hyperactivity_impulsivity (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.; 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.; 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).; 조용한 활동 곤란: 여가 활동을 조용히 하지 못하는 경우가 잦다.; 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.; 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.; 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.; 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.; 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 있음
+체크리스트 그룹: inattention (관계=must_include, 요구개수=5, 충족개수=8, 커버리지=1.0)
+확인된 근거:
+  - 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.
+  - 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.
+  - 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.
+  - 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.
+  - 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.
+  - 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.
+  - 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).
+  - 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).
+체크리스트 그룹: hyperactivity_impulsivity (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A46:B46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D002_S001_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D002_S001_P003__qwen3-235b_kor.xlsx
@@ -776,6 +776,11 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -823,11 +828,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A46:B46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D002_S001_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D002_S001_P003__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.32</v>
+        <v>0.3666</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.5216</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.9167</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
